--- a/04_Figures/F3/c_data/F3.xlsx
+++ b/04_Figures/F3/c_data/F3.xlsx
@@ -470,7 +470,7 @@
     <t>02_HRvLR/02_Set_Contrasts/c_data/set_tests.rds</t>
   </si>
   <si>
-    <t>30db8bea525624e038076e732efccd5f</t>
+    <t>913e33734a82439181cc7dfdb9ea1917</t>
   </si>
   <si>
     <t>BiocManager</t>
